--- a/database_penyimpanan_aman/database_status_pembayaran.xlsx
+++ b/database_penyimpanan_aman/database_status_pembayaran.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,14 +477,24 @@
           <t>Update Terakhir</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Nomor Faktur Pajak</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Durasi Riil Hari</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/II/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -494,12 +504,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -507,40 +517,38 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>24150000</v>
+        <v>73803990</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Belum Dibayar</t>
+          <t>Lunas</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Diserahkan Langsung pada tanggal 27 Agustus 2026</t>
-        </is>
-      </c>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-08-27 12:06:55</t>
-        </is>
-      </c>
+          <t>2026-09-10 20:39:33</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/VIII/2026</t>
+          <t>036/BSS-JOB/II/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -550,12 +558,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,11 +571,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2180000</v>
+        <v>51177360</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -576,19 +584,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Sudah dibayar Lunas</t>
-        </is>
-      </c>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-08-27 12:11:09</t>
-        </is>
-      </c>
+          <t>2026-09-10 20:40:45</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -596,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/IX/2026</t>
+          <t>126/BSS-JOB/VI/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -606,12 +612,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -619,11 +625,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>46683000</v>
+        <v>69192500</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -635,15 +641,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Invoice telah diserahkan ke Pelanggan tgl 1 September 2026</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-08-27 14:01:29</t>
-        </is>
+          <t>2026-09-10 22:29:26</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>4002600226111627</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>127/BSS-JOB/VI/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>8900078849999999</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Belum Dibayar</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-09-10 22:31:41</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>03002600226134177</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_status_pembayaran.xlsx
+++ b/database_penyimpanan_aman/database_status_pembayaran.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>126/BSS-JOB/VI/2026</t>
+          <t>127/BSS-JOB/VI/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>69192500</v>
+        <v>890007884.9999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -644,11 +644,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-10 22:29:26</t>
+          <t>2026-09-10 22:31:41</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>4002600226111627</v>
+        <v>3002600226134177</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -662,7 +662,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>127/BSS-JOB/VI/2026</t>
+          <t>126/BSS-JOB/VI/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -689,31 +689,35 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8900078849999999</v>
+        <v>6919250</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Belum Dibayar</t>
+          <t>Lunas</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lunas terbayar di pootong pph  </t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-10 22:31:41</t>
+          <t>2026-09-11 10:40:22</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>03002600226134177</t>
+          <t>4002600226111627.0</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
